--- a/target/classes/Data.xlsx
+++ b/target/classes/Data.xlsx
@@ -1,23 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asaloumi\IdeaProjects\CTS\src\main\resources\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6998369-211A-4864-910F-851CA4DEC6E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="Sheet1"/>
-    <sheet r:id="rId2" sheetId="2" name="old"/>
-    <sheet r:id="rId3" sheetId="3" name="Sheet3"/>
-    <sheet r:id="rId4" sheetId="4" name="Sheet2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="old" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="0" iterate="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="238">
   <si>
     <t>Employee ID</t>
   </si>
@@ -736,7 +742,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.000000"/>
   </numFmts>
@@ -750,7 +756,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFffffff"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
@@ -762,7 +768,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFffffff"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -782,7 +788,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFffffff"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -814,31 +820,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFff8080"/>
+        <fgColor rgb="FFFF8080"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFf2f2f2"/>
+        <fgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00b0f0"/>
+        <fgColor rgb="FF00B0F0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFa02b93"/>
+        <fgColor rgb="FFA02B93"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFd9d9d9"/>
+        <fgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -848,16 +854,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </left>
       <right style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </right>
       <top style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </bottom>
       <diagonal/>
     </border>
@@ -884,10 +890,10 @@
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </bottom>
       <diagonal/>
     </border>
@@ -900,10 +906,10 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </left>
       <right style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </right>
       <top style="thin">
         <color rgb="FF000000"/>
@@ -915,7 +921,7 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </left>
       <right style="thin">
         <color rgb="FF000000"/>
@@ -930,7 +936,7 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </left>
       <right style="thin">
         <color rgb="FF000000"/>
@@ -939,7 +945,7 @@
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </bottom>
       <diagonal/>
     </border>
@@ -954,19 +960,19 @@
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </left>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
@@ -981,7 +987,7 @@
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
@@ -993,10 +999,10 @@
         <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </right>
       <top style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
@@ -1008,7 +1014,7 @@
         <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </right>
       <top style="thin">
         <color rgb="FF000000"/>
@@ -1018,181 +1024,152 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFc6c6c6"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFc6c6c6"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+  <cellXfs count="35">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="5" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="6" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="6" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="7" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="7" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="7" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="7" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="7" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="7" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="5" applyBorder="1" fontId="8" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="8" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="6" applyBorder="1" fontId="7" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="6" applyBorder="1" fontId="7" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="6" applyBorder="1" fontId="7" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="7" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="6" applyBorder="1" fontId="7" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="7" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="7" applyBorder="1" fontId="7" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="7" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="8" applyBorder="1" fontId="7" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="7" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="9" applyBorder="1" fontId="5" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="10" applyBorder="1" fontId="6" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="11" applyBorder="1" fontId="6" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="6" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="7" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="12" applyBorder="1" fontId="7" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="7" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="7" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="12" applyBorder="1" fontId="7" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="7" applyBorder="1" fontId="7" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="13" applyBorder="1" fontId="7" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="8" applyBorder="1" fontId="7" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="7" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:B76" displayName="Table1" name="Table1" id="1" totalsRowShown="0">
-  <autoFilter ref="A1:B76"/>
-  <tableColumns count="2">
-    <tableColumn name="Grupo" id="1"/>
-    <tableColumn name="Grupo2" id="2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{0A87A749-EE48-4944-9691-6F82B3A13744}" name="Table24" displayName="Table24" ref="A1:C31" totalsRowShown="0">
+  <autoFilter ref="A1:C31" xr:uid="{0A87A749-EE48-4944-9691-6F82B3A13744}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C31">
+    <sortCondition ref="B1:B31"/>
+  </sortState>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{B88AA2B1-51A2-4C09-B2FD-898E70F1DCD0}" name="Group ID"/>
+    <tableColumn id="2" xr3:uid="{9D6CA084-A926-4166-9BE6-0D002ED964F1}" name="COGS EUR FY25"/>
+    <tableColumn id="3" xr3:uid="{EFE616E6-3AB7-479B-80AD-03C1C820E746}" name="COGS EUR FY26"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showColumnStripes="0" showRowStripes="1" showLastColumn="0" showFirstColumn="0"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:C85" displayName="Table2" name="Table2" id="2" totalsRowShown="0">
-  <autoFilter ref="A1:C85"/>
-  <tableColumns count="3">
-    <tableColumn name="Group ID" id="1"/>
-    <tableColumn name="COGS EUR FY25" id="2"/>
-    <tableColumn name="COGS EUR FY26" id="3"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table1" displayName="Table1" ref="A1:B76" totalsRowShown="0">
+  <autoFilter ref="A1:B76" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Grupo"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Grupo2"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showColumnStripes="0" showRowStripes="1" showLastColumn="0" showFirstColumn="0"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -1201,10 +1178,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="0E2841"/>
@@ -1242,71 +1219,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1334,7 +1311,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -1357,11 +1334,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -1370,13 +1347,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -1386,7 +1363,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -1395,7 +1372,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -1404,7 +1381,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -1412,10 +1389,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -1480,933 +1457,352 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C85"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" style="19" width="15.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="40" width="17.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="21" width="17.005" customWidth="1" bestFit="1"/>
-  </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="30" t="s">
+    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="29" t="s">
         <v>95</v>
       </c>
-      <c r="C1" s="32" t="s">
+      <c r="C1" s="30" t="s">
         <v>96</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="24" t="s">
-        <v>138</v>
+    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="23" t="s">
+        <v>236</v>
       </c>
       <c r="B2" s="33">
-        <v>25.0344</v>
+        <v>1</v>
       </c>
       <c r="C2" s="34">
-        <v>25.91</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="25" t="s">
-        <v>139</v>
-      </c>
-      <c r="B3" s="35">
-        <v>30.5976</v>
-      </c>
-      <c r="C3" s="36">
-        <v>31.67</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="24" t="s">
-        <v>140</v>
-      </c>
-      <c r="B4" s="33">
-        <v>38.9424</v>
-      </c>
-      <c r="C4" s="34">
-        <v>40.31</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="25" t="s">
-        <v>141</v>
-      </c>
-      <c r="B5" s="35">
-        <v>46.36</v>
-      </c>
-      <c r="C5" s="36">
-        <v>47.98</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="25" t="s">
-        <v>133</v>
-      </c>
-      <c r="B6" s="35">
-        <v>6.3977</v>
-      </c>
-      <c r="C6" s="36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="B3" s="33">
+        <v>6.3976800000000003</v>
+      </c>
+      <c r="C3" s="34">
         <v>6.62</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="24" t="s">
-        <v>134</v>
+    <row r="4" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="B4" s="31">
+        <v>9.3647200000000002</v>
+      </c>
+      <c r="C4" s="32">
+        <v>9.69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="23" t="s">
+        <v>142</v>
+      </c>
+      <c r="B5" s="33">
+        <v>10.199199999999999</v>
+      </c>
+      <c r="C5" s="34">
+        <v>10.56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="B6" s="33">
+        <v>12.517200000000001</v>
+      </c>
+      <c r="C6" s="34">
+        <v>12.96</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="23" t="s">
+        <v>99</v>
       </c>
       <c r="B7" s="33">
-        <v>10.1992</v>
+        <v>13.53712</v>
       </c>
       <c r="C7" s="34">
-        <v>10.56</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="25" t="s">
-        <v>135</v>
-      </c>
-      <c r="B8" s="35">
-        <v>14.8352</v>
-      </c>
-      <c r="C8" s="36">
-        <v>15.35</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="24" t="s">
-        <v>136</v>
+        <v>14.01</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="22" t="s">
+        <v>143</v>
+      </c>
+      <c r="B8" s="31">
+        <v>13.815300000000001</v>
+      </c>
+      <c r="C8" s="32">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="23" t="s">
+        <v>108</v>
       </c>
       <c r="B9" s="33">
-        <v>18.544</v>
+        <v>14.093439999999999</v>
       </c>
       <c r="C9" s="34">
-        <v>19.19</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
-      <c r="A10" s="25" t="s">
-        <v>137</v>
-      </c>
-      <c r="B10" s="35">
-        <v>21.3256</v>
-      </c>
-      <c r="C10" s="36">
-        <v>22.07</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
-      <c r="A11" s="24" t="s">
-        <v>111</v>
-      </c>
-      <c r="B11" s="33">
-        <v>24.5708</v>
-      </c>
-      <c r="C11" s="34">
-        <v>25.43</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
-      <c r="A12" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="B12" s="35">
-        <v>29.6704</v>
-      </c>
-      <c r="C12" s="36">
-        <v>30.71</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="24" t="s">
-        <v>113</v>
-      </c>
-      <c r="B13" s="33">
-        <v>38.9424</v>
-      </c>
-      <c r="C13" s="34">
-        <v>40.31</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
-      <c r="A14" s="25" t="s">
-        <v>114</v>
-      </c>
-      <c r="B14" s="35">
-        <v>46.36</v>
-      </c>
-      <c r="C14" s="36">
-        <v>47.98</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
-      <c r="A15" s="25" t="s">
-        <v>106</v>
-      </c>
-      <c r="B15" s="35">
-        <v>6.3977</v>
-      </c>
-      <c r="C15" s="36">
-        <v>6.62</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
-      <c r="A16" s="24" t="s">
-        <v>107</v>
-      </c>
-      <c r="B16" s="33">
-        <v>10.1992</v>
-      </c>
-      <c r="C16" s="34">
-        <v>10.56</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
-      <c r="A17" s="25" t="s">
-        <v>108</v>
-      </c>
-      <c r="B17" s="35">
-        <v>14.09344</v>
-      </c>
-      <c r="C17" s="36">
         <v>14.59</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
-      <c r="A18" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="B18" s="33">
-        <v>18.0804</v>
-      </c>
-      <c r="C18" s="34">
+    <row r="10" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="B10" s="31">
+        <v>16.596900000000002</v>
+      </c>
+      <c r="C10" s="32">
+        <v>17.18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="B11" s="31">
+        <v>17.153199999999998</v>
+      </c>
+      <c r="C11" s="32">
+        <v>17.75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="B12" s="33">
+        <v>17.895</v>
+      </c>
+      <c r="C12" s="34">
+        <v>21.59</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="B13" s="31">
+        <v>18.080400000000001</v>
+      </c>
+      <c r="C13" s="32">
         <v>18.71</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
-      <c r="A19" s="25" t="s">
-        <v>110</v>
-      </c>
-      <c r="B19" s="35">
-        <v>20.3984</v>
-      </c>
-      <c r="C19" s="36">
-        <v>21.11</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
-      <c r="A20" s="24" t="s">
-        <v>165</v>
+    <row r="14" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="B14" s="33">
+        <v>19.934799999999999</v>
+      </c>
+      <c r="C14" s="34">
+        <v>20.63</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="B15" s="33">
+        <v>20.769300000000001</v>
+      </c>
+      <c r="C15" s="34">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="22" t="s">
+        <v>145</v>
+      </c>
+      <c r="B16" s="31">
+        <v>20.861999999999998</v>
+      </c>
+      <c r="C16" s="32">
+        <v>26.39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="B17" s="31">
+        <v>23.829000000000001</v>
+      </c>
+      <c r="C17" s="32">
+        <v>24.66</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="B18" s="31">
+        <v>24.2926</v>
+      </c>
+      <c r="C18" s="32">
+        <v>25.14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="23" t="s">
+        <v>237</v>
+      </c>
+      <c r="B19" s="33">
+        <v>25</v>
+      </c>
+      <c r="C19" s="34">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="23" t="s">
+        <v>146</v>
       </c>
       <c r="B20" s="33">
-        <v>29.6704</v>
+        <v>25.498000000000001</v>
       </c>
       <c r="C20" s="34">
-        <v>30.71</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
-      <c r="A21" s="25" t="s">
-        <v>166</v>
-      </c>
-      <c r="B21" s="35">
-        <v>35.2336</v>
-      </c>
-      <c r="C21" s="36">
-        <v>36.47</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
-      <c r="A22" s="24" t="s">
-        <v>167</v>
+        <v>32.619999999999997</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="23" t="s">
+        <v>103</v>
+      </c>
+      <c r="B21" s="33">
+        <v>27.4451</v>
+      </c>
+      <c r="C21" s="34">
+        <v>28.41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="23" t="s">
+        <v>130</v>
       </c>
       <c r="B22" s="33">
-        <v>39.8696</v>
+        <v>31.524799999999999</v>
       </c>
       <c r="C22" s="34">
-        <v>41.27</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
-      <c r="A23" s="25" t="s">
-        <v>168</v>
-      </c>
-      <c r="B23" s="35">
-        <v>46.36</v>
-      </c>
-      <c r="C23" s="36">
-        <v>47.98</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
-      <c r="A24" s="25" t="s">
-        <v>160</v>
-      </c>
-      <c r="B24" s="35">
-        <v>6.3977</v>
-      </c>
-      <c r="C24" s="36">
-        <v>6.62</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
-      <c r="A25" s="24" t="s">
-        <v>161</v>
-      </c>
-      <c r="B25" s="33">
-        <v>10.1992</v>
-      </c>
-      <c r="C25" s="34">
-        <v>10.56</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
-      <c r="A26" s="25" t="s">
-        <v>162</v>
-      </c>
-      <c r="B26" s="35">
-        <v>13.8153</v>
-      </c>
-      <c r="C26" s="36">
-        <v>14.3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
-      <c r="A27" s="24" t="s">
-        <v>163</v>
+        <v>32.630000000000003</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="B23" s="31">
+        <v>37.088000000000001</v>
+      </c>
+      <c r="C23" s="32">
+        <v>38.39</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="B24" s="33">
+        <v>37.551600000000001</v>
+      </c>
+      <c r="C24" s="34">
+        <v>45.58</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="B25" s="31">
+        <v>38.0152</v>
+      </c>
+      <c r="C25" s="32">
+        <v>39.35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="B26" s="31">
+        <v>38.4788</v>
+      </c>
+      <c r="C26" s="32">
+        <v>39.83</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="23" t="s">
+        <v>132</v>
       </c>
       <c r="B27" s="33">
-        <v>19.4712</v>
+        <v>41.723999999999997</v>
       </c>
       <c r="C27" s="34">
-        <v>20.15</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
-      <c r="A28" s="25" t="s">
-        <v>164</v>
-      </c>
-      <c r="B28" s="35">
-        <v>24.1072</v>
-      </c>
-      <c r="C28" s="36">
-        <v>24.95</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
-      <c r="A29" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="B29" s="33">
-        <v>24.2926</v>
-      </c>
-      <c r="C29" s="34">
-        <v>25.14</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
-      <c r="A30" s="25" t="s">
-        <v>103</v>
-      </c>
-      <c r="B30" s="35">
-        <v>27.4451</v>
-      </c>
-      <c r="C30" s="36">
-        <v>28.41</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
-      <c r="A31" s="24" t="s">
-        <v>104</v>
+        <v>43.18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="B28" s="33">
+        <v>42.651200000000003</v>
+      </c>
+      <c r="C28" s="34">
+        <v>44.14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="22" t="s">
+        <v>149</v>
+      </c>
+      <c r="B29" s="31">
+        <v>44.042000000000002</v>
+      </c>
+      <c r="C29" s="32">
+        <v>52.79</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="23" t="s">
+        <v>235</v>
+      </c>
+      <c r="B30" s="33">
+        <v>50</v>
+      </c>
+      <c r="C30" s="34">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="23" t="s">
+        <v>150</v>
       </c>
       <c r="B31" s="33">
-        <v>38.0152</v>
+        <v>50.996000000000002</v>
       </c>
       <c r="C31" s="34">
-        <v>39.35</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
-      <c r="A32" s="25" t="s">
-        <v>105</v>
-      </c>
-      <c r="B32" s="35">
-        <v>42.6512</v>
-      </c>
-      <c r="C32" s="36">
-        <v>44.14</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
-      <c r="A33" s="25" t="s">
-        <v>97</v>
-      </c>
-      <c r="B33" s="35">
-        <v>6.39768</v>
-      </c>
-      <c r="C33" s="36">
-        <v>6.62</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
-      <c r="A34" s="24" t="s">
-        <v>98</v>
-      </c>
-      <c r="B34" s="33">
-        <v>9.36472</v>
-      </c>
-      <c r="C34" s="34">
-        <v>9.69</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
-      <c r="A35" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="B35" s="35">
-        <v>13.53712</v>
-      </c>
-      <c r="C35" s="36">
-        <v>14.01</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
-      <c r="A36" s="24" t="s">
-        <v>100</v>
-      </c>
-      <c r="B36" s="33">
-        <v>17.1532</v>
-      </c>
-      <c r="C36" s="34">
-        <v>17.75</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
-      <c r="A37" s="25" t="s">
-        <v>101</v>
-      </c>
-      <c r="B37" s="35">
-        <v>20.7693</v>
-      </c>
-      <c r="C37" s="36">
-        <v>21.5</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
-      <c r="A38" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="B38" s="33">
-        <v>31.5248</v>
-      </c>
-      <c r="C38" s="34">
-        <v>38.86</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
-      <c r="A39" s="25" t="s">
-        <v>148</v>
-      </c>
-      <c r="B39" s="35">
-        <v>37.5516</v>
-      </c>
-      <c r="C39" s="36">
-        <v>45.58</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
-      <c r="A40" s="24" t="s">
-        <v>149</v>
-      </c>
-      <c r="B40" s="33">
-        <v>44.042</v>
-      </c>
-      <c r="C40" s="34">
-        <v>52.79</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
-      <c r="A41" s="25" t="s">
-        <v>150</v>
-      </c>
-      <c r="B41" s="35">
-        <v>50.996</v>
-      </c>
-      <c r="C41" s="36">
         <v>57.96</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
-      <c r="A42" s="25" t="s">
-        <v>142</v>
-      </c>
-      <c r="B42" s="35">
-        <v>10.1992</v>
-      </c>
-      <c r="C42" s="36">
-        <v>10.56</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
-      <c r="A43" s="24" t="s">
-        <v>143</v>
-      </c>
-      <c r="B43" s="33">
-        <v>13.8153</v>
-      </c>
-      <c r="C43" s="34">
-        <v>14.3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
-      <c r="A44" s="25" t="s">
-        <v>144</v>
-      </c>
-      <c r="B44" s="35">
-        <v>17.895</v>
-      </c>
-      <c r="C44" s="36">
-        <v>21.59</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
-      <c r="A45" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="B45" s="33">
-        <v>20.862</v>
-      </c>
-      <c r="C45" s="34">
-        <v>26.39</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
-      <c r="A46" s="25" t="s">
-        <v>146</v>
-      </c>
-      <c r="B46" s="35">
-        <v>25.498</v>
-      </c>
-      <c r="C46" s="36">
-        <v>32.62</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
-      <c r="A47" s="24" t="s">
-        <v>174</v>
-      </c>
-      <c r="B47" s="33"/>
-      <c r="C47" s="34">
-        <v>42</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
-      <c r="A48" s="25" t="s">
-        <v>175</v>
-      </c>
-      <c r="B48" s="35"/>
-      <c r="C48" s="36">
-        <v>48</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
-      <c r="A49" s="24" t="s">
-        <v>176</v>
-      </c>
-      <c r="B49" s="33"/>
-      <c r="C49" s="34">
-        <v>55</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
-      <c r="A50" s="25" t="s">
-        <v>177</v>
-      </c>
-      <c r="B50" s="35"/>
-      <c r="C50" s="36">
-        <v>65</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
-      <c r="A51" s="25" t="s">
-        <v>169</v>
-      </c>
-      <c r="B51" s="35"/>
-      <c r="C51" s="36">
-        <v>11.5</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
-      <c r="A52" s="24" t="s">
-        <v>170</v>
-      </c>
-      <c r="B52" s="33"/>
-      <c r="C52" s="34">
-        <v>19</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
-      <c r="A53" s="25" t="s">
-        <v>171</v>
-      </c>
-      <c r="B53" s="35"/>
-      <c r="C53" s="36">
-        <v>27</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
-      <c r="A54" s="24" t="s">
-        <v>172</v>
-      </c>
-      <c r="B54" s="33"/>
-      <c r="C54" s="34">
-        <v>35</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
-      <c r="A55" s="25" t="s">
-        <v>173</v>
-      </c>
-      <c r="B55" s="35"/>
-      <c r="C55" s="36">
-        <v>38</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
-      <c r="A56" s="24" t="s">
-        <v>120</v>
-      </c>
-      <c r="B56" s="33">
-        <v>25.0344</v>
-      </c>
-      <c r="C56" s="34">
-        <v>25.91</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
-      <c r="A57" s="25" t="s">
-        <v>121</v>
-      </c>
-      <c r="B57" s="35">
-        <v>31.0612</v>
-      </c>
-      <c r="C57" s="36">
-        <v>32.15</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
-      <c r="A58" s="24" t="s">
-        <v>122</v>
-      </c>
-      <c r="B58" s="33">
-        <v>39.406</v>
-      </c>
-      <c r="C58" s="34">
-        <v>40.79</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
-      <c r="A59" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="B59" s="35">
-        <v>44.042</v>
-      </c>
-      <c r="C59" s="36">
-        <v>45.58</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
-      <c r="A60" s="25" t="s">
-        <v>115</v>
-      </c>
-      <c r="B60" s="35">
-        <v>6.3977</v>
-      </c>
-      <c r="C60" s="36">
-        <v>6.62</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
-      <c r="A61" s="24" t="s">
-        <v>116</v>
-      </c>
-      <c r="B61" s="33">
-        <v>9.921</v>
-      </c>
-      <c r="C61" s="34">
-        <v>10.27</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
-      <c r="A62" s="25" t="s">
-        <v>117</v>
-      </c>
-      <c r="B62" s="35">
-        <v>14.3716</v>
-      </c>
-      <c r="C62" s="36">
-        <v>14.87</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
-      <c r="A63" s="24" t="s">
-        <v>118</v>
-      </c>
-      <c r="B63" s="33">
-        <v>18.0804</v>
-      </c>
-      <c r="C63" s="34">
-        <v>18.71</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
-      <c r="A64" s="25" t="s">
-        <v>119</v>
-      </c>
-      <c r="B64" s="35">
-        <v>21.3256</v>
-      </c>
-      <c r="C64" s="36">
-        <v>22.07</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="19.5">
-      <c r="A65" s="24" t="s">
-        <v>156</v>
-      </c>
-      <c r="B65" s="33">
-        <v>25.9616</v>
-      </c>
-      <c r="C65" s="34">
-        <v>26.87</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
-      <c r="A66" s="25" t="s">
-        <v>157</v>
-      </c>
-      <c r="B66" s="35">
-        <v>30.5976</v>
-      </c>
-      <c r="C66" s="36">
-        <v>31.67</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
-      <c r="A67" s="24" t="s">
-        <v>158</v>
-      </c>
-      <c r="B67" s="33">
-        <v>38.4788</v>
-      </c>
-      <c r="C67" s="34">
-        <v>39.83</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
-      <c r="A68" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="B68" s="35">
-        <v>41.724</v>
-      </c>
-      <c r="C68" s="36">
-        <v>43.18</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
-      <c r="A69" s="25" t="s">
-        <v>151</v>
-      </c>
-      <c r="B69" s="35">
-        <v>6.3977</v>
-      </c>
-      <c r="C69" s="36">
-        <v>6.62</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
-      <c r="A70" s="24" t="s">
-        <v>152</v>
-      </c>
-      <c r="B70" s="33">
-        <v>10.6628</v>
-      </c>
-      <c r="C70" s="34">
-        <v>11.04</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
-      <c r="A71" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="B71" s="35">
-        <v>13.908</v>
-      </c>
-      <c r="C71" s="36">
-        <v>14.39</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
-      <c r="A72" s="24" t="s">
-        <v>154</v>
-      </c>
-      <c r="B72" s="33">
-        <v>16.9678</v>
-      </c>
-      <c r="C72" s="34">
-        <v>17.56</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
-      <c r="A73" s="25" t="s">
-        <v>155</v>
-      </c>
-      <c r="B73" s="35">
-        <v>20.3057</v>
-      </c>
-      <c r="C73" s="36">
-        <v>21.02</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
-      <c r="A74" s="24" t="s">
-        <v>129</v>
-      </c>
-      <c r="B74" s="33">
-        <v>23.829</v>
-      </c>
-      <c r="C74" s="34">
-        <v>24.66</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
-      <c r="A75" s="25" t="s">
-        <v>130</v>
-      </c>
-      <c r="B75" s="35">
-        <v>31.5248</v>
-      </c>
-      <c r="C75" s="36">
-        <v>32.63</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
-      <c r="A76" s="24" t="s">
-        <v>131</v>
-      </c>
-      <c r="B76" s="33">
-        <v>37.088</v>
-      </c>
-      <c r="C76" s="34">
-        <v>38.39</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
-      <c r="A77" s="25" t="s">
-        <v>132</v>
-      </c>
-      <c r="B77" s="35">
-        <v>41.724</v>
-      </c>
-      <c r="C77" s="36">
-        <v>43.18</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
-      <c r="A78" s="25" t="s">
-        <v>124</v>
-      </c>
-      <c r="B78" s="35">
-        <v>6.3977</v>
-      </c>
-      <c r="C78" s="36">
-        <v>6.62</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
-      <c r="A79" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="B79" s="33">
-        <v>9.55016</v>
-      </c>
-      <c r="C79" s="34">
-        <v>9.88</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
-      <c r="A80" s="25" t="s">
-        <v>126</v>
-      </c>
-      <c r="B80" s="35">
-        <v>12.5172</v>
-      </c>
-      <c r="C80" s="36">
-        <v>12.96</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
-      <c r="A81" s="24" t="s">
-        <v>127</v>
-      </c>
-      <c r="B81" s="33">
-        <v>16.5969</v>
-      </c>
-      <c r="C81" s="34">
-        <v>17.18</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
-      <c r="A82" s="37" t="s">
-        <v>128</v>
-      </c>
-      <c r="B82" s="35">
-        <v>19.9348</v>
-      </c>
-      <c r="C82" s="38">
-        <v>20.63</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
-      <c r="A83" s="25" t="s">
-        <v>237</v>
-      </c>
-      <c r="B83" s="35">
-        <v>25</v>
-      </c>
-      <c r="C83" s="16">
-        <v>25</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
-      <c r="A84" s="25" t="s">
-        <v>235</v>
-      </c>
-      <c r="B84" s="35">
-        <v>50</v>
-      </c>
-      <c r="C84" s="16">
-        <v>50</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
-      <c r="A85" s="37" t="s">
-        <v>236</v>
-      </c>
-      <c r="B85" s="39">
-        <v>1</v>
-      </c>
-      <c r="C85" s="29">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2418,648 +1814,648 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B82"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="19" width="12.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="20" width="9.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.85546875" style="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="22" t="s">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="21" t="s">
         <v>178</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="24" t="s">
+    <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="22" t="s">
         <v>179</v>
       </c>
       <c r="B2" s="18">
-        <v>25.0344</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="25" t="s">
+        <v>25.034400000000002</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="23" t="s">
         <v>180</v>
       </c>
       <c r="B3" s="16">
         <v>30.5976</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="24" t="s">
+    <row r="4" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="22" t="s">
         <v>181</v>
       </c>
       <c r="B4" s="18">
-        <v>38.9424</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="25" t="s">
+        <v>38.942399999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="23" t="s">
         <v>182</v>
       </c>
       <c r="B5" s="16">
         <v>46.36</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="25" t="s">
+    <row r="6" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="23" t="s">
         <v>183</v>
       </c>
       <c r="B6" s="16">
-        <v>6.3977</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="24" t="s">
+        <v>6.3977000000000004</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="22" t="s">
         <v>184</v>
       </c>
       <c r="B7" s="18">
-        <v>10.1992</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="25" t="s">
+        <v>10.199199999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="23" t="s">
         <v>185</v>
       </c>
       <c r="B8" s="16">
         <v>14.8352</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="24" t="s">
+    <row r="9" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="22" t="s">
         <v>186</v>
       </c>
       <c r="B9" s="18">
         <v>18.544</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
-      <c r="A10" s="25" t="s">
+    <row r="10" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="23" t="s">
         <v>187</v>
       </c>
       <c r="B10" s="16">
-        <v>21.3256</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
-      <c r="A11" s="24" t="s">
+        <v>21.325600000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="22" t="s">
         <v>29</v>
       </c>
       <c r="B11" s="18">
-        <v>24.5708</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
-      <c r="A12" s="25" t="s">
+        <v>24.570799999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="23" t="s">
         <v>188</v>
       </c>
       <c r="B12" s="16">
-        <v>29.6704</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="24" t="s">
+        <v>29.670400000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="22" t="s">
         <v>189</v>
       </c>
       <c r="B13" s="18">
-        <v>38.9424</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
-      <c r="A14" s="25" t="s">
+        <v>38.942399999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="23" t="s">
         <v>190</v>
       </c>
       <c r="B14" s="16">
         <v>46.36</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
-      <c r="A15" s="25" t="s">
+    <row r="15" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="23" t="s">
         <v>191</v>
       </c>
       <c r="B15" s="16">
-        <v>6.3977</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
-      <c r="A16" s="24" t="s">
+        <v>6.3977000000000004</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="22" t="s">
         <v>15</v>
       </c>
       <c r="B16" s="18">
-        <v>10.1992</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
-      <c r="A17" s="25" t="s">
+        <v>10.199199999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="23" t="s">
         <v>8</v>
       </c>
       <c r="B17" s="16">
-        <v>14.09344</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
-      <c r="A18" s="24" t="s">
+        <v>14.093439999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="22" t="s">
         <v>6</v>
       </c>
       <c r="B18" s="18">
-        <v>18.0804</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
-      <c r="A19" s="25" t="s">
+        <v>18.080400000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="23" t="s">
         <v>22</v>
       </c>
       <c r="B19" s="16">
-        <v>20.3984</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
-      <c r="A20" s="24" t="s">
+        <v>20.398399999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="22" t="s">
         <v>192</v>
       </c>
       <c r="B20" s="18">
-        <v>29.6704</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
-      <c r="A21" s="25" t="s">
+        <v>29.670400000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="23" t="s">
         <v>193</v>
       </c>
       <c r="B21" s="16">
-        <v>35.2336</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
-      <c r="A22" s="24" t="s">
+        <v>35.233600000000003</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="22" t="s">
         <v>194</v>
       </c>
       <c r="B22" s="18">
-        <v>39.8696</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
-      <c r="A23" s="25" t="s">
+        <v>39.869599999999998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="23" t="s">
         <v>195</v>
       </c>
       <c r="B23" s="16">
         <v>46.36</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
-      <c r="A24" s="25" t="s">
+    <row r="24" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="23" t="s">
         <v>196</v>
       </c>
       <c r="B24" s="16">
-        <v>6.3977</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
-      <c r="A25" s="24" t="s">
+        <v>6.3977000000000004</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="22" t="s">
         <v>197</v>
       </c>
       <c r="B25" s="18">
-        <v>10.1992</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
-      <c r="A26" s="25" t="s">
+        <v>10.199199999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="23" t="s">
         <v>198</v>
       </c>
       <c r="B26" s="16">
-        <v>13.8153</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
-      <c r="A27" s="24" t="s">
+        <v>13.815300000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="22" t="s">
         <v>199</v>
       </c>
       <c r="B27" s="18">
         <v>19.4712</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
-      <c r="A28" s="25" t="s">
+    <row r="28" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="23" t="s">
         <v>200</v>
       </c>
       <c r="B28" s="16">
-        <v>24.1072</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
-      <c r="A29" s="24" t="s">
+        <v>24.107199999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="22" t="s">
         <v>12</v>
       </c>
       <c r="B29" s="18">
         <v>24.2926</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
-      <c r="A30" s="25" t="s">
+    <row r="30" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="23" t="s">
         <v>201</v>
       </c>
       <c r="B30" s="16">
         <v>27.4451</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
-      <c r="A31" s="24" t="s">
+    <row r="31" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="22" t="s">
         <v>202</v>
       </c>
       <c r="B31" s="18">
         <v>38.0152</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
-      <c r="A32" s="25" t="s">
+    <row r="32" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="23" t="s">
         <v>203</v>
       </c>
       <c r="B32" s="16">
-        <v>42.6512</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
-      <c r="A33" s="25" t="s">
+        <v>42.651200000000003</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="23" t="s">
         <v>19</v>
       </c>
       <c r="B33" s="16">
-        <v>6.39768</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
-      <c r="A34" s="24" t="s">
+        <v>6.3976800000000003</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="22" t="s">
         <v>25</v>
       </c>
       <c r="B34" s="18">
-        <v>9.36472</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
-      <c r="A35" s="25" t="s">
+        <v>9.3647200000000002</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="23" t="s">
         <v>4</v>
       </c>
       <c r="B35" s="16">
         <v>13.53712</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
-      <c r="A36" s="24" t="s">
+    <row r="36" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="22" t="s">
         <v>46</v>
       </c>
       <c r="B36" s="18">
-        <v>17.1532</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
-      <c r="A37" s="25" t="s">
+        <v>17.153199999999998</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="23" t="s">
         <v>204</v>
       </c>
       <c r="B37" s="16">
-        <v>20.7693</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
-      <c r="A38" s="24" t="s">
+        <v>20.769300000000001</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="22" t="s">
         <v>205</v>
       </c>
       <c r="B38" s="18">
-        <v>31.5248</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
-      <c r="A39" s="25" t="s">
+        <v>31.524799999999999</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="23" t="s">
         <v>88</v>
       </c>
       <c r="B39" s="16">
-        <v>37.5516</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
-      <c r="A40" s="24" t="s">
+        <v>37.551600000000001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="22" t="s">
         <v>206</v>
       </c>
       <c r="B40" s="18">
-        <v>44.042</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
-      <c r="A41" s="25" t="s">
+        <v>44.042000000000002</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="23" t="s">
         <v>207</v>
       </c>
       <c r="B41" s="16">
-        <v>50.996</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
-      <c r="A42" s="25" t="s">
+        <v>50.996000000000002</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="23" t="s">
         <v>208</v>
       </c>
       <c r="B42" s="16">
-        <v>10.1992</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
-      <c r="A43" s="24" t="s">
+        <v>10.199199999999999</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="22" t="s">
         <v>209</v>
       </c>
       <c r="B43" s="18">
-        <v>13.8153</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
-      <c r="A44" s="25" t="s">
+        <v>13.815300000000001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="23" t="s">
         <v>210</v>
       </c>
       <c r="B44" s="16">
         <v>17.895</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
-      <c r="A45" s="24" t="s">
+    <row r="45" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="22" t="s">
         <v>211</v>
       </c>
       <c r="B45" s="18">
-        <v>20.862</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
-      <c r="A46" s="25" t="s">
+        <v>20.861999999999998</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="23" t="s">
         <v>212</v>
       </c>
       <c r="B46" s="16">
-        <v>25.498</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
-      <c r="A47" s="24" t="s">
+        <v>25.498000000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="22" t="s">
         <v>213</v>
       </c>
       <c r="B47" s="18">
-        <v>25.0344</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
-      <c r="A48" s="25" t="s">
+        <v>25.034400000000002</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="23" t="s">
         <v>214</v>
       </c>
       <c r="B48" s="16">
-        <v>31.0612</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
-      <c r="A49" s="24" t="s">
+        <v>31.061199999999999</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="22" t="s">
         <v>215</v>
       </c>
       <c r="B49" s="18">
-        <v>39.406</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
-      <c r="A50" s="25" t="s">
+        <v>39.405999999999999</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="23" t="s">
         <v>216</v>
       </c>
       <c r="B50" s="16">
-        <v>44.042</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
-      <c r="A51" s="25" t="s">
+        <v>44.042000000000002</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="23" t="s">
         <v>217</v>
       </c>
       <c r="B51" s="16">
-        <v>6.3977</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
-      <c r="A52" s="24" t="s">
+        <v>6.3977000000000004</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="22" t="s">
         <v>218</v>
       </c>
       <c r="B52" s="18">
-        <v>9.921</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
-      <c r="A53" s="25" t="s">
+        <v>9.9209999999999994</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="23" t="s">
         <v>78</v>
       </c>
       <c r="B53" s="16">
-        <v>14.3716</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
-      <c r="A54" s="24" t="s">
+        <v>14.371600000000001</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="22" t="s">
         <v>219</v>
       </c>
       <c r="B54" s="18">
-        <v>18.0804</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
-      <c r="A55" s="25" t="s">
+        <v>18.080400000000001</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="23" t="s">
         <v>67</v>
       </c>
       <c r="B55" s="16">
-        <v>21.3256</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
-      <c r="A56" s="24" t="s">
+        <v>21.325600000000001</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="22" t="s">
         <v>220</v>
       </c>
       <c r="B56" s="18">
-        <v>25.9616</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
-      <c r="A57" s="25" t="s">
+        <v>25.961600000000001</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="23" t="s">
         <v>10</v>
       </c>
       <c r="B57" s="16">
         <v>30.5976</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
-      <c r="A58" s="24" t="s">
+    <row r="58" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="22" t="s">
         <v>221</v>
       </c>
       <c r="B58" s="18">
         <v>38.4788</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
-      <c r="A59" s="25" t="s">
+    <row r="59" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="23" t="s">
         <v>222</v>
       </c>
       <c r="B59" s="16">
-        <v>41.724</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
-      <c r="A60" s="25" t="s">
+        <v>41.723999999999997</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="23" t="s">
         <v>223</v>
       </c>
       <c r="B60" s="16">
-        <v>6.3977</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
-      <c r="A61" s="24" t="s">
+        <v>6.3977000000000004</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="22" t="s">
         <v>224</v>
       </c>
       <c r="B61" s="18">
-        <v>10.6628</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
-      <c r="A62" s="25" t="s">
+        <v>10.662800000000001</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="23" t="s">
         <v>225</v>
       </c>
       <c r="B62" s="16">
-        <v>13.908</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
-      <c r="A63" s="24" t="s">
+        <v>13.907999999999999</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="22" t="s">
         <v>226</v>
       </c>
       <c r="B63" s="18">
         <v>16.9678</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
-      <c r="A64" s="25" t="s">
+    <row r="64" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="23" t="s">
         <v>227</v>
       </c>
       <c r="B64" s="16">
-        <v>20.3057</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
-      <c r="A65" s="24" t="s">
+        <v>20.305700000000002</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="22" t="s">
         <v>228</v>
       </c>
       <c r="B65" s="18">
-        <v>23.829</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
-      <c r="A66" s="25" t="s">
+        <v>23.829000000000001</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="23" t="s">
         <v>229</v>
       </c>
       <c r="B66" s="16">
-        <v>31.5248</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
-      <c r="A67" s="24" t="s">
+        <v>31.524799999999999</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="22" t="s">
         <v>230</v>
       </c>
       <c r="B67" s="18">
-        <v>37.088</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
-      <c r="A68" s="25" t="s">
+        <v>37.088000000000001</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="23" t="s">
         <v>231</v>
       </c>
       <c r="B68" s="16">
-        <v>41.724</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
-      <c r="A69" s="25" t="s">
+        <v>41.723999999999997</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="23" t="s">
         <v>232</v>
       </c>
       <c r="B69" s="16">
-        <v>6.3977</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
-      <c r="A70" s="24" t="s">
+        <v>6.3977000000000004</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="22" t="s">
         <v>86</v>
       </c>
       <c r="B70" s="18">
         <v>9.55016</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
-      <c r="A71" s="25" t="s">
+    <row r="71" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="23" t="s">
         <v>75</v>
       </c>
       <c r="B71" s="16">
-        <v>12.5172</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
-      <c r="A72" s="24" t="s">
+        <v>12.517200000000001</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="22" t="s">
         <v>73</v>
       </c>
       <c r="B72" s="18">
-        <v>16.5969</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
-      <c r="A73" s="25" t="s">
+        <v>16.596900000000002</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="23" t="s">
         <v>233</v>
       </c>
       <c r="B73" s="16">
-        <v>19.9348</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
-      <c r="A74" s="24" t="s">
+        <v>19.934799999999999</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="22" t="s">
         <v>234</v>
       </c>
       <c r="B74" s="18">
         <v>25</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
-      <c r="A75" s="25" t="s">
+    <row r="75" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="23" t="s">
         <v>235</v>
       </c>
       <c r="B75" s="16">
         <v>50</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
-      <c r="A76" s="24" t="s">
+    <row r="76" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="22" t="s">
         <v>236</v>
       </c>
       <c r="B76" s="18">
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
-      <c r="A77" s="26"/>
+    <row r="77" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="24"/>
       <c r="B77" s="16"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
-      <c r="A78" s="26"/>
+    <row r="78" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="24"/>
       <c r="B78" s="16"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
-      <c r="A79" s="27"/>
+    <row r="79" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="25"/>
       <c r="B79" s="18"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
-      <c r="A80" s="26"/>
+    <row r="80" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="24"/>
       <c r="B80" s="16"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
-      <c r="A81" s="27"/>
+    <row r="81" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="25"/>
       <c r="B81" s="18"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
-      <c r="A82" s="28"/>
-      <c r="B82" s="29"/>
+    <row r="82" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="26"/>
+      <c r="B82" s="27"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3070,19 +2466,19 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C82"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="20" width="14.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="21" width="14.719285714285713" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.7109375" style="19" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" style="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
         <v>94</v>
       </c>
@@ -3093,7 +2489,7 @@
         <v>96</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
         <v>97</v>
       </c>
@@ -3104,7 +2500,7 @@
         <v>6.62</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
         <v>98</v>
       </c>
@@ -3115,7 +2511,7 @@
         <v>9.69</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row r="4" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
         <v>99</v>
       </c>
@@ -3126,18 +2522,18 @@
         <v>14.01</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row r="5" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
         <v>100</v>
       </c>
       <c r="B5" s="18">
-        <v>17.15</v>
+        <v>17.149999999999999</v>
       </c>
       <c r="C5" s="18">
         <v>17.75</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row r="6" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>101</v>
       </c>
@@ -3148,7 +2544,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row r="7" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
         <v>102</v>
       </c>
@@ -3159,7 +2555,7 @@
         <v>25.14</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row r="8" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
         <v>103</v>
       </c>
@@ -3170,18 +2566,18 @@
         <v>28.41</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row r="9" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>104</v>
       </c>
       <c r="B9" s="18">
-        <v>38.02</v>
+        <v>38.020000000000003</v>
       </c>
       <c r="C9" s="18">
         <v>39.35</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row r="10" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
         <v>105</v>
       </c>
@@ -3192,7 +2588,7 @@
         <v>44.14</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+    <row r="11" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
         <v>106</v>
       </c>
@@ -3203,18 +2599,18 @@
         <v>6.62</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+    <row r="12" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
         <v>107</v>
       </c>
       <c r="B12" s="18">
-        <v>10.2</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="C12" s="18">
         <v>10.56</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+    <row r="13" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
         <v>108</v>
       </c>
@@ -3225,29 +2621,29 @@
         <v>14.59</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+    <row r="14" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
         <v>109</v>
       </c>
       <c r="B14" s="18">
-        <v>18.08</v>
+        <v>18.079999999999998</v>
       </c>
       <c r="C14" s="18">
         <v>18.71</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+    <row r="15" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
         <v>110</v>
       </c>
       <c r="B15" s="16">
-        <v>20.4</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="C15" s="16">
         <v>21.11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+    <row r="16" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>111</v>
       </c>
@@ -3258,7 +2654,7 @@
         <v>25.43</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+    <row r="17" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="15" t="s">
         <v>112</v>
       </c>
@@ -3269,7 +2665,7 @@
         <v>30.71</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+    <row r="18" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="s">
         <v>113</v>
       </c>
@@ -3280,7 +2676,7 @@
         <v>40.31</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+    <row r="19" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="15" t="s">
         <v>114</v>
       </c>
@@ -3291,7 +2687,7 @@
         <v>47.98</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+    <row r="20" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
         <v>115</v>
       </c>
@@ -3302,7 +2698,7 @@
         <v>6.62</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+    <row r="21" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>116</v>
       </c>
@@ -3313,7 +2709,7 @@
         <v>10.27</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+    <row r="22" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
         <v>117</v>
       </c>
@@ -3324,18 +2720,18 @@
         <v>14.87</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+    <row r="23" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
         <v>118</v>
       </c>
       <c r="B23" s="18">
-        <v>18.08</v>
+        <v>18.079999999999998</v>
       </c>
       <c r="C23" s="18">
         <v>18.71</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+    <row r="24" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
         <v>119</v>
       </c>
@@ -3346,7 +2742,7 @@
         <v>22.07</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+    <row r="25" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="17" t="s">
         <v>120</v>
       </c>
@@ -3357,7 +2753,7 @@
         <v>25.91</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+    <row r="26" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
         <v>121</v>
       </c>
@@ -3368,18 +2764,18 @@
         <v>32.15</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
+    <row r="27" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="17" t="s">
         <v>122</v>
       </c>
       <c r="B27" s="18">
-        <v>39.41</v>
+        <v>39.409999999999997</v>
       </c>
       <c r="C27" s="18">
         <v>40.79</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
+    <row r="28" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
         <v>123</v>
       </c>
@@ -3390,7 +2786,7 @@
         <v>45.58</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
+    <row r="29" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
         <v>124</v>
       </c>
@@ -3401,18 +2797,18 @@
         <v>6.62</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
+    <row r="30" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="17" t="s">
         <v>125</v>
       </c>
       <c r="B30" s="18">
-        <v>9.55</v>
+        <v>9.5500000000000007</v>
       </c>
       <c r="C30" s="18">
-        <v>9.88</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
+        <v>9.8800000000000008</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="15" t="s">
         <v>126</v>
       </c>
@@ -3423,18 +2819,18 @@
         <v>12.96</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
+    <row r="32" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
         <v>127</v>
       </c>
       <c r="B32" s="18">
-        <v>16.6</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="C32" s="18">
         <v>17.18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
+    <row r="33" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="15" t="s">
         <v>128</v>
       </c>
@@ -3445,7 +2841,7 @@
         <v>20.63</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
+    <row r="34" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="17" t="s">
         <v>129</v>
       </c>
@@ -3456,7 +2852,7 @@
         <v>24.66</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
+    <row r="35" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="15" t="s">
         <v>130</v>
       </c>
@@ -3464,21 +2860,21 @@
         <v>31.52</v>
       </c>
       <c r="C35" s="16">
-        <v>32.63</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
+        <v>32.630000000000003</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="17" t="s">
         <v>131</v>
       </c>
       <c r="B36" s="18">
-        <v>37.09</v>
+        <v>37.090000000000003</v>
       </c>
       <c r="C36" s="18">
         <v>38.39</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
+    <row r="37" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="15" t="s">
         <v>132</v>
       </c>
@@ -3489,7 +2885,7 @@
         <v>43.18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
+    <row r="38" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="15" t="s">
         <v>133</v>
       </c>
@@ -3500,18 +2896,18 @@
         <v>6.62</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
+    <row r="39" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="17" t="s">
         <v>134</v>
       </c>
       <c r="B39" s="18">
-        <v>10.2</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="C39" s="18">
         <v>10.56</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
+    <row r="40" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="15" t="s">
         <v>135</v>
       </c>
@@ -3522,7 +2918,7 @@
         <v>15.35</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
+    <row r="41" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="17" t="s">
         <v>136</v>
       </c>
@@ -3530,10 +2926,10 @@
         <v>18.54</v>
       </c>
       <c r="C41" s="18">
-        <v>19.19</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
+        <v>19.190000000000001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="15" t="s">
         <v>137</v>
       </c>
@@ -3544,7 +2940,7 @@
         <v>22.07</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
+    <row r="43" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="17" t="s">
         <v>138</v>
       </c>
@@ -3555,7 +2951,7 @@
         <v>25.91</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
+    <row r="44" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="15" t="s">
         <v>139</v>
       </c>
@@ -3566,7 +2962,7 @@
         <v>31.67</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
+    <row r="45" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="17" t="s">
         <v>140</v>
       </c>
@@ -3577,7 +2973,7 @@
         <v>40.31</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
+    <row r="46" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="15" t="s">
         <v>141</v>
       </c>
@@ -3588,18 +2984,18 @@
         <v>47.98</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
+    <row r="47" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="15" t="s">
         <v>142</v>
       </c>
       <c r="B47" s="16">
-        <v>10.2</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="C47" s="16">
         <v>10.56</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
+    <row r="48" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="17" t="s">
         <v>143</v>
       </c>
@@ -3610,7 +3006,7 @@
         <v>14.3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
+    <row r="49" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="15" t="s">
         <v>144</v>
       </c>
@@ -3621,7 +3017,7 @@
         <v>21.59</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
+    <row r="50" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="17" t="s">
         <v>145</v>
       </c>
@@ -3632,7 +3028,7 @@
         <v>26.39</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
+    <row r="51" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="15" t="s">
         <v>146</v>
       </c>
@@ -3640,21 +3036,21 @@
         <v>31.52</v>
       </c>
       <c r="C51" s="16">
-        <v>32.62</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
+        <v>32.619999999999997</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="17" t="s">
         <v>147</v>
       </c>
       <c r="B52" s="18">
-        <v>37.55</v>
+        <v>37.549999999999997</v>
       </c>
       <c r="C52" s="18">
         <v>38.86</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
+    <row r="53" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="15" t="s">
         <v>148</v>
       </c>
@@ -3665,7 +3061,7 @@
         <v>45.58</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
+    <row r="54" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="17" t="s">
         <v>149</v>
       </c>
@@ -3676,7 +3072,7 @@
         <v>52.79</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
+    <row r="55" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="15" t="s">
         <v>150</v>
       </c>
@@ -3687,7 +3083,7 @@
         <v>57.96</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
+    <row r="56" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="15" t="s">
         <v>151</v>
       </c>
@@ -3698,7 +3094,7 @@
         <v>6.62</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
+    <row r="57" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="17" t="s">
         <v>152</v>
       </c>
@@ -3709,7 +3105,7 @@
         <v>11.04</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
+    <row r="58" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="15" t="s">
         <v>153</v>
       </c>
@@ -3720,7 +3116,7 @@
         <v>14.39</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
+    <row r="59" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="17" t="s">
         <v>154</v>
       </c>
@@ -3728,21 +3124,21 @@
         <v>16.97</v>
       </c>
       <c r="C59" s="18">
-        <v>17.56</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
+        <v>17.559999999999999</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="15" t="s">
         <v>155</v>
       </c>
       <c r="B60" s="16">
-        <v>20.31</v>
+        <v>20.309999999999999</v>
       </c>
       <c r="C60" s="16">
         <v>21.02</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
+    <row r="61" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="17" t="s">
         <v>156</v>
       </c>
@@ -3753,7 +3149,7 @@
         <v>26.87</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
+    <row r="62" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="15" t="s">
         <v>157</v>
       </c>
@@ -3764,18 +3160,18 @@
         <v>31.67</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
+    <row r="63" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="17" t="s">
         <v>158</v>
       </c>
       <c r="B63" s="18">
-        <v>38.48</v>
+        <v>38.479999999999997</v>
       </c>
       <c r="C63" s="18">
         <v>39.83</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
+    <row r="64" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="15" t="s">
         <v>159</v>
       </c>
@@ -3786,7 +3182,7 @@
         <v>43.18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
+    <row r="65" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="15" t="s">
         <v>160</v>
       </c>
@@ -3797,18 +3193,18 @@
         <v>6.62</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
+    <row r="66" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="17" t="s">
         <v>161</v>
       </c>
       <c r="B66" s="18">
-        <v>10.2</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="C66" s="18">
         <v>10.56</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
+    <row r="67" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="15" t="s">
         <v>162</v>
       </c>
@@ -3819,7 +3215,7 @@
         <v>14.3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
+    <row r="68" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="17" t="s">
         <v>163</v>
       </c>
@@ -3827,10 +3223,10 @@
         <v>19.47</v>
       </c>
       <c r="C68" s="18">
-        <v>20.15</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
+        <v>20.149999999999999</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="15" t="s">
         <v>164</v>
       </c>
@@ -3841,7 +3237,7 @@
         <v>24.95</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
+    <row r="70" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="17" t="s">
         <v>165</v>
       </c>
@@ -3852,29 +3248,29 @@
         <v>30.71</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
+    <row r="71" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="15" t="s">
         <v>166</v>
       </c>
       <c r="B71" s="16">
-        <v>35.23</v>
+        <v>35.229999999999997</v>
       </c>
       <c r="C71" s="16">
         <v>36.47</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
+    <row r="72" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="17" t="s">
         <v>167</v>
       </c>
       <c r="B72" s="18">
-        <v>39.87</v>
+        <v>39.869999999999997</v>
       </c>
       <c r="C72" s="18">
         <v>41.27</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
+    <row r="73" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="15" t="s">
         <v>168</v>
       </c>
@@ -3885,7 +3281,7 @@
         <v>47.98</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
+    <row r="74" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="15" t="s">
         <v>169</v>
       </c>
@@ -3894,7 +3290,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
+    <row r="75" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="17" t="s">
         <v>170</v>
       </c>
@@ -3903,7 +3299,7 @@
         <v>19</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
+    <row r="76" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="15" t="s">
         <v>171</v>
       </c>
@@ -3912,7 +3308,7 @@
         <v>27</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
+    <row r="77" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="17" t="s">
         <v>172</v>
       </c>
@@ -3921,7 +3317,7 @@
         <v>35</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
+    <row r="78" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="15" t="s">
         <v>173</v>
       </c>
@@ -3930,7 +3326,7 @@
         <v>38</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
+    <row r="79" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="17" t="s">
         <v>174</v>
       </c>
@@ -3939,7 +3335,7 @@
         <v>42</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
+    <row r="80" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="15" t="s">
         <v>175</v>
       </c>
@@ -3948,7 +3344,7 @@
         <v>48</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
+    <row r="81" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="17" t="s">
         <v>176</v>
       </c>
@@ -3957,7 +3353,7 @@
         <v>55</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
+    <row r="82" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="15" t="s">
         <v>177</v>
       </c>
@@ -3972,19 +3368,19 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C76"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="10" width="11.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="11" width="32.86214285714286" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="12" width="22.14785714285714" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="11.7109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.85546875" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.140625" style="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3995,7 +3391,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>213407</v>
       </c>
@@ -4006,7 +3402,7 @@
         <v>4</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>222205</v>
       </c>
@@ -4017,7 +3413,7 @@
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row r="4" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>232362</v>
       </c>
@@ -4028,7 +3424,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row r="5" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>193507</v>
       </c>
@@ -4039,7 +3435,7 @@
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row r="6" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>223691</v>
       </c>
@@ -4050,7 +3446,7 @@
         <v>12</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row r="7" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>234127</v>
       </c>
@@ -4061,7 +3457,7 @@
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row r="8" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>218008</v>
       </c>
@@ -4072,7 +3468,7 @@
         <v>15</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row r="9" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>238916</v>
       </c>
@@ -4083,7 +3479,7 @@
         <v>15</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row r="10" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>238422</v>
       </c>
@@ -4094,7 +3490,7 @@
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+    <row r="11" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>193507</v>
       </c>
@@ -4105,7 +3501,7 @@
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+    <row r="12" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>258310</v>
       </c>
@@ -4116,7 +3512,7 @@
         <v>19</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+    <row r="13" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>256435</v>
       </c>
@@ -4127,7 +3523,7 @@
         <v>15</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+    <row r="14" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>257631</v>
       </c>
@@ -4138,7 +3534,7 @@
         <v>22</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+    <row r="15" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>256455</v>
       </c>
@@ -4149,7 +3545,7 @@
         <v>15</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+    <row r="16" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>244747</v>
       </c>
@@ -4160,7 +3556,7 @@
         <v>25</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+    <row r="17" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>256438</v>
       </c>
@@ -4171,7 +3567,7 @@
         <v>15</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+    <row r="18" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>201782</v>
       </c>
@@ -4182,7 +3578,7 @@
         <v>22</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+    <row r="19" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>208094</v>
       </c>
@@ -4193,7 +3589,7 @@
         <v>29</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+    <row r="20" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>229412</v>
       </c>
@@ -4204,7 +3600,7 @@
         <v>15</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+    <row r="21" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>212031</v>
       </c>
@@ -4215,7 +3611,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+    <row r="22" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>207349</v>
       </c>
@@ -4226,7 +3622,7 @@
         <v>29</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+    <row r="23" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>261099</v>
       </c>
@@ -4237,7 +3633,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+    <row r="24" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>229471</v>
       </c>
@@ -4248,7 +3644,7 @@
         <v>25</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+    <row r="25" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>219022</v>
       </c>
@@ -4259,7 +3655,7 @@
         <v>15</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+    <row r="26" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <v>270203</v>
       </c>
@@ -4270,7 +3666,7 @@
         <v>19</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
+    <row r="27" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>229406</v>
       </c>
@@ -4281,7 +3677,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
+    <row r="28" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
         <v>238374</v>
       </c>
@@ -4292,7 +3688,7 @@
         <v>15</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
+    <row r="29" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <v>256454</v>
       </c>
@@ -4303,7 +3699,7 @@
         <v>15</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
+    <row r="30" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
         <v>275136</v>
       </c>
@@ -4314,7 +3710,7 @@
         <v>19</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
+    <row r="31" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <v>156580</v>
       </c>
@@ -4325,7 +3721,7 @@
         <v>4</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
+    <row r="32" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
         <v>229403</v>
       </c>
@@ -4336,7 +3732,7 @@
         <v>25</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
+    <row r="33" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <v>276878</v>
       </c>
@@ -4347,7 +3743,7 @@
         <v>19</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
+    <row r="34" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
         <v>286026</v>
       </c>
@@ -4358,7 +3754,7 @@
         <v>4</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
+    <row r="35" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <v>162617</v>
       </c>
@@ -4369,7 +3765,7 @@
         <v>46</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
+    <row r="36" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
         <v>283959</v>
       </c>
@@ -4380,7 +3776,7 @@
         <v>19</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
+    <row r="37" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <v>279163</v>
       </c>
@@ -4391,7 +3787,7 @@
         <v>19</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
+    <row r="38" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <v>238502</v>
       </c>
@@ -4402,7 +3798,7 @@
         <v>46</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
+    <row r="39" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
         <v>191889</v>
       </c>
@@ -4413,7 +3809,7 @@
         <v>46</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
+    <row r="40" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <v>197747</v>
       </c>
@@ -4424,7 +3820,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
+    <row r="41" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <v>224251</v>
       </c>
@@ -4435,7 +3831,7 @@
         <v>4</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
+    <row r="42" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
         <v>234875</v>
       </c>
@@ -4446,7 +3842,7 @@
         <v>4</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
+    <row r="43" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <v>220562</v>
       </c>
@@ -4457,7 +3853,7 @@
         <v>25</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
+    <row r="44" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
         <v>233234</v>
       </c>
@@ -4468,7 +3864,7 @@
         <v>22</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
+    <row r="45" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
         <v>244754</v>
       </c>
@@ -4479,7 +3875,7 @@
         <v>19</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
+    <row r="46" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
         <v>260396</v>
       </c>
@@ -4490,7 +3886,7 @@
         <v>19</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
+    <row r="47" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
         <v>258860</v>
       </c>
@@ -4501,7 +3897,7 @@
         <v>19</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
+    <row r="48" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
         <v>244757</v>
       </c>
@@ -4512,7 +3908,7 @@
         <v>25</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
+    <row r="49" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
         <v>177606</v>
       </c>
@@ -4523,7 +3919,7 @@
         <v>4</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
+    <row r="50" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
         <v>257561</v>
       </c>
@@ -4534,7 +3930,7 @@
         <v>19</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
+    <row r="51" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
         <v>190916</v>
       </c>
@@ -4545,7 +3941,7 @@
         <v>25</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
+    <row r="52" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
         <v>190884</v>
       </c>
@@ -4556,7 +3952,7 @@
         <v>25</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
+    <row r="53" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="4">
         <v>244758</v>
       </c>
@@ -4567,7 +3963,7 @@
         <v>25</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
+    <row r="54" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="4">
         <v>286024</v>
       </c>
@@ -4578,7 +3974,7 @@
         <v>25</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
+    <row r="55" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
         <v>221243</v>
       </c>
@@ -4589,7 +3985,7 @@
         <v>67</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
+    <row r="56" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="4">
         <v>188286</v>
       </c>
@@ -4600,7 +3996,7 @@
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
+    <row r="57" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="4">
         <v>275057</v>
       </c>
@@ -4611,7 +4007,7 @@
         <v>19</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
+    <row r="58" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="4">
         <v>188286</v>
       </c>
@@ -4622,7 +4018,7 @@
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
+    <row r="59" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="4">
         <v>279942</v>
       </c>
@@ -4633,7 +4029,7 @@
         <v>19</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
+    <row r="60" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="4">
         <v>190923</v>
       </c>
@@ -4644,7 +4040,7 @@
         <v>25</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
+    <row r="61" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="4">
         <v>216964</v>
       </c>
@@ -4655,7 +4051,7 @@
         <v>73</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
+    <row r="62" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="4">
         <v>257328</v>
       </c>
@@ -4666,7 +4062,7 @@
         <v>75</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
+    <row r="63" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="4">
         <v>234877</v>
       </c>
@@ -4677,7 +4073,7 @@
         <v>29</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
+    <row r="64" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="4">
         <v>188286</v>
       </c>
@@ -4688,7 +4084,7 @@
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
+    <row r="65" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="4">
         <v>196428</v>
       </c>
@@ -4699,7 +4095,7 @@
         <v>78</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
+    <row r="66" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="4">
         <v>270819</v>
       </c>
@@ -4710,7 +4106,7 @@
         <v>22</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
+    <row r="67" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="4">
         <v>188286</v>
       </c>
@@ -4721,7 +4117,7 @@
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
+    <row r="68" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="4">
         <v>246691</v>
       </c>
@@ -4732,7 +4128,7 @@
         <v>22</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
+    <row r="69" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="4">
         <v>286025</v>
       </c>
@@ -4743,7 +4139,7 @@
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
+    <row r="70" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="4">
         <v>168857</v>
       </c>
@@ -4754,7 +4150,7 @@
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
+    <row r="71" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="4">
         <v>233946</v>
       </c>
@@ -4765,7 +4161,7 @@
         <v>29</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
+    <row r="72" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="4">
         <v>229622</v>
       </c>
@@ -4776,7 +4172,7 @@
         <v>46</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
+    <row r="73" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="4">
         <v>179599</v>
       </c>
@@ -4787,7 +4183,7 @@
         <v>86</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
+    <row r="74" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="4">
         <v>285831</v>
       </c>
@@ -4798,7 +4194,7 @@
         <v>88</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
+    <row r="75" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
         <v>89</v>
       </c>
@@ -4809,7 +4205,7 @@
         <v>91</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
+    <row r="76" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="8" t="s">
         <v>92</v>
       </c>
